--- a/PAM_VERDE_BASELINE_ENDLINE_NAMPULA_BEIRA.xlsx
+++ b/PAM_VERDE_BASELINE_ENDLINE_NAMPULA_BEIRA.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="11_ADF9AC6AED3094B38E73D6675675FF5AA44B5F92" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8262D7C9-F5F5-4DEC-AAF6-75A4876A09E1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAM_VERDE_BASELINE_ENDLINE_Repo" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PAM_VERDE_BASELINE_ENDLINE_Repo!$A$1:$CU$117</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -44690,10 +44690,20 @@
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
@@ -44704,18 +44714,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
     <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
     <xsd:element name="properties">
@@ -44788,7 +44789,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -44811,7 +44812,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -44830,7 +44831,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -44858,8 +44859,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -44949,6 +44950,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B700D00C-450D-44DF-BF78-06F2624130F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB0BD64F-7ED1-4180-B11A-E5C02362ADC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -44959,14 +44968,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B700D00C-450D-44DF-BF78-06F2624130F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED089CFB-3409-4A82-903D-AA0B48E8AC98}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39EFEACE-8068-4040-8D02-5270907C9848}"/>
 </file>
--- a/PAM_VERDE_BASELINE_ENDLINE_NAMPULA_BEIRA.xlsx
+++ b/PAM_VERDE_BASELINE_ENDLINE_NAMPULA_BEIRA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/Pam_Verde/2026/Baseline_Endline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_ADF9AC6AED3094B38E73D6675675FF5AA44B5F92" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8262D7C9-F5F5-4DEC-AAF6-75A4876A09E1}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_ADF9AC6AED3094B38E73D6675675FF5AA44B5F92" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C9EBD19-E5EA-4F3B-A3B1-EA4D860B53EA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44695,28 +44695,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
     <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
     <xsd:element name="properties">
@@ -44789,7 +44769,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -44812,7 +44792,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -44831,7 +44811,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -44859,8 +44839,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -44949,12 +44929,28 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B700D00C-450D-44DF-BF78-06F2624130F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{690A4718-9113-4F28-A901-06F8C5AEBA52}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -44969,5 +44965,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39EFEACE-8068-4040-8D02-5270907C9848}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B700D00C-450D-44DF-BF78-06F2624130F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>